--- a/experiments/prompt-tuning/hc+ft/Results/Cardd_qwen_greedy/cardd_prompt01.xlsx
+++ b/experiments/prompt-tuning/hc+ft/Results/Cardd_qwen_greedy/cardd_prompt01.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UshariRanasinghe\Desktop\Projects\vlm-research\experiments\prompt-tuning\hc+ft\Results\Cardd_qwen_greedy\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3381DD2-9F48-484C-B692-23CA8BFC50A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="3980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>sample_index</t>
   </si>
@@ -104,13 +110,28 @@
   </si>
   <si>
     <t>The car exhibits significant rust and corrosion, particularly on the lower body panels and wheel arches. The paint is peeling and chipped extensively across the body, revealing the underlying metal. The wheel itself shows signs of wear and dirt accumulation. The overall condition of the car is poor, with extensive damage to the bodywork and paint.</t>
+  </si>
+  <si>
+    <t>Describe &amp;&amp;damage 12 sedan drive’ this !!image.,</t>
+  </si>
+  <si>
+    <t>Explain the visible damage to this vehicle. Question: What areas are affected and how severe is the damage? Answer:,</t>
+  </si>
+  <si>
+    <t>You are an insurance claims assessor. Provide a detailed description of the car’s condition.,</t>
+  </si>
+  <si>
+    <t>This \&lt;part\_1&gt; of the car has \&lt;damage_type\_1&gt; . The severity appears to be \&lt;severity\_1&gt;. Additional notes: \&lt;text\_1&gt;.,</t>
+  </si>
+  <si>
+    <t>Describe the damage in the following format – Damage Type: \_\_\_; Affected Part: \_\_\_; Severity: \_\_\_; Notes: \_\_\_</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +194,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -193,7 +222,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -231,7 +266,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -269,7 +310,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -307,7 +354,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -345,7 +398,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -383,7 +442,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -421,7 +486,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -459,7 +530,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -497,7 +574,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -535,7 +618,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -604,7 +693,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,9 +725,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -670,6 +777,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -845,11 +970,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:Q12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="13.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +1006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>0</v>
       </c>
@@ -895,7 +1023,7 @@
         <v>0.8640059232711792</v>
       </c>
       <c r="G2">
-        <v>0.2857142857142858</v>
+        <v>0.28571428571428581</v>
       </c>
       <c r="H2">
         <v>2.768791513988019</v>
@@ -904,10 +1032,10 @@
         <v>7099.93896484375</v>
       </c>
       <c r="J2">
-        <v>26.6966724395752</v>
+        <v>26.696672439575199</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -921,22 +1049,22 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.8056271076202393</v>
+        <v>0.80562710762023926</v>
       </c>
       <c r="G3">
         <v>0.3</v>
       </c>
       <c r="H3">
-        <v>3.03668957182627</v>
+        <v>3.0366895718262699</v>
       </c>
       <c r="I3">
         <v>7108.06396484375</v>
       </c>
       <c r="J3">
-        <v>6.188923597335815</v>
+        <v>6.1889235973358154</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -950,22 +1078,37 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.7969993948936462</v>
+        <v>0.79699939489364624</v>
       </c>
       <c r="G4">
-        <v>0.4090909090909091</v>
+        <v>0.40909090909090912</v>
       </c>
       <c r="H4">
-        <v>3.329262252616139</v>
+        <v>3.3292622526161391</v>
       </c>
       <c r="I4">
         <v>7108.06396484375</v>
       </c>
       <c r="J4">
-        <v>5.05748176574707</v>
+        <v>5.0574817657470703</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -979,22 +1122,40 @@
         <v>23</v>
       </c>
       <c r="F5">
-        <v>0.8586803078651428</v>
+        <v>0.85868030786514282</v>
       </c>
       <c r="G5">
-        <v>0.2916666666666667</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="H5">
-        <v>2.398215408052011</v>
+        <v>2.3982154080520108</v>
       </c>
       <c r="I5">
         <v>7137.7939453125</v>
       </c>
       <c r="J5">
-        <v>4.345563411712646</v>
+        <v>4.3455634117126456</v>
+      </c>
+      <c r="L5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>0.79240441984600496</v>
+      </c>
+      <c r="N5">
+        <v>0.27387204657945208</v>
+      </c>
+      <c r="O5">
+        <v>2.6293797159250847</v>
+      </c>
+      <c r="P5">
+        <v>7119.8074001736113</v>
+      </c>
+      <c r="Q5">
+        <v>4.8154215812683105</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1008,7 +1169,7 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>0.62485671043396</v>
+        <v>0.62485671043395996</v>
       </c>
       <c r="G6">
         <v>0.1276595744680851</v>
@@ -1020,10 +1181,28 @@
         <v>7114.06005859375</v>
       </c>
       <c r="J6">
-        <v>5.459974527359009</v>
+        <v>5.4599745273590088</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0.77070834570460844</v>
+      </c>
+      <c r="N6">
+        <v>0.2444260415969608</v>
+      </c>
+      <c r="O6">
+        <v>2.6336176155935651</v>
+      </c>
+      <c r="P6">
+        <v>7122.114095052083</v>
+      </c>
+      <c r="Q6">
+        <v>4.6153825653923883</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1037,10 +1216,10 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0.6794235706329346</v>
+        <v>0.67942357063293457</v>
       </c>
       <c r="G7">
-        <v>0.2222222222222222</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="H7">
         <v>1.798518894100898</v>
@@ -1049,10 +1228,28 @@
         <v>7114.06005859375</v>
       </c>
       <c r="J7">
-        <v>3.980842590332031</v>
+        <v>3.9808425903320308</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>0.767037034034729</v>
+      </c>
+      <c r="N7">
+        <v>0.21499189211065842</v>
+      </c>
+      <c r="O7">
+        <v>2.3810153864553163</v>
+      </c>
+      <c r="P7">
+        <v>7124.4450412326387</v>
+      </c>
+      <c r="Q7">
+        <v>5.1184017923143177</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1066,7 +1263,7 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>0.8625762462615967</v>
+        <v>0.86257624626159668</v>
       </c>
       <c r="G8">
         <v>0.2461538461538462</v>
@@ -1078,10 +1275,28 @@
         <v>7114.06005859375</v>
       </c>
       <c r="J8">
-        <v>5.972065925598145</v>
+        <v>5.9720659255981454</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>0.74933966000874841</v>
+      </c>
+      <c r="N8">
+        <v>0.24725409668707984</v>
+      </c>
+      <c r="O8">
+        <v>2.5714902119992398</v>
+      </c>
+      <c r="P8">
+        <v>7123.5218641493057</v>
+      </c>
+      <c r="Q8">
+        <v>5.1008058124118385</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1095,22 +1310,40 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>0.8804655075073242</v>
+        <v>0.88046550750732422</v>
       </c>
       <c r="G9">
-        <v>0.4186046511627907</v>
+        <v>0.41860465116279072</v>
       </c>
       <c r="H9">
-        <v>3.295029953316322</v>
+        <v>3.2950299533163219</v>
       </c>
       <c r="I9">
         <v>7106.57666015625</v>
       </c>
       <c r="J9">
-        <v>3.377384185791016</v>
+        <v>3.3773841857910161</v>
+      </c>
+      <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9">
+        <v>0.78590805663002861</v>
+      </c>
+      <c r="N9">
+        <v>0.26579234004765923</v>
+      </c>
+      <c r="O9">
+        <v>2.5928781295231405</v>
+      </c>
+      <c r="P9">
+        <v>7127.5415581597226</v>
+      </c>
+      <c r="Q9">
+        <v>4.7540760040283203</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1124,22 +1357,40 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0.8721975684165955</v>
+        <v>0.87219756841659546</v>
       </c>
       <c r="G10">
-        <v>0.1923076923076923</v>
+        <v>0.19230769230769229</v>
       </c>
       <c r="H10">
-        <v>2.810338674016591</v>
+        <v>2.8103386740165912</v>
       </c>
       <c r="I10">
         <v>7137.7939453125</v>
       </c>
       <c r="J10">
-        <v>4.176807403564453</v>
+        <v>4.1768074035644531</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10">
+        <v>0.75971902741326225</v>
+      </c>
+      <c r="N10">
+        <v>0.23393559443979614</v>
+      </c>
+      <c r="O10">
+        <v>2.5460863637042119</v>
+      </c>
+      <c r="P10">
+        <v>7127.224934895833</v>
+      </c>
+      <c r="Q10">
+        <v>4.5276411904229059</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1153,10 +1404,10 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.750813364982605</v>
+        <v>0.75081336498260498</v>
       </c>
       <c r="G11">
-        <v>0.2571428571428572</v>
+        <v>0.25714285714285717</v>
       </c>
       <c r="H11">
         <v>3.240807011840376</v>
@@ -1165,11 +1416,34 @@
         <v>7137.7939453125</v>
       </c>
       <c r="J11">
-        <v>4.779750823974609</v>
+        <v>4.7797508239746094</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <f>AVERAGE(F3:F11)</f>
+        <v>0.79240441984600496</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:J12" si="0">AVERAGE(G3:G11)</f>
+        <v>0.27387204657945208</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>2.6293797159250847</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>7119.8074001736113</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>4.8154215812683105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>